--- a/output/pdf_financials_xlsx/BET.xlsx
+++ b/output/pdf_financials_xlsx/BET.xlsx
@@ -2534,10 +2534,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.021019</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.030809</v>
       </c>
       <c r="D92" s="3" t="n">
         <v>0.420042</v>
@@ -7109,7 +7109,11 @@
           <t>Reserves 5 30,694</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
@@ -7783,7 +7787,11 @@
           <t>Reserves 5</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E102" s="5" t="n">
         <v>0.021019</v>
       </c>

--- a/output/pdf_financials_xlsx/BET.xlsx
+++ b/output/pdf_financials_xlsx/BET.xlsx
@@ -685,16 +685,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.00194</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.00194</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.0009</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.08723400000000001</v>
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
@@ -1061,16 +1061,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.187695</v>
+        <v>-0.189635</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.187695</v>
+        <v>-0.189635</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-20.197035</v>
+        <v>-20.197935</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-25.475646</v>
+        <v>-25.56288</v>
       </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
@@ -1109,16 +1109,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.187695</v>
+        <v>-0.189635</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.187695</v>
+        <v>-0.189635</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-20.126979</v>
+        <v>-20.127879</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-25.229355</v>
+        <v>-25.316589</v>
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-350.3982831563002</v>
+        <v>-350.4139516008711</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-129.9585234727165</v>
+        <v>-130.4078731226231</v>
       </c>
       <c r="F30" s="1" t="inlineStr">
         <is>
@@ -12089,7 +12089,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -13650,7 +13650,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -14718,7 +14718,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E269" s="5" t="n">

--- a/output/pdf_financials_xlsx/BET.xlsx
+++ b/output/pdf_financials_xlsx/BET.xlsx
@@ -571,7 +571,7 @@
         <v>0.047679</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.092886</v>
+        <v>0.152886</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -2727,7 +2727,7 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.002322</v>
       </c>
       <c r="C101" s="3" t="n">
         <v>-0.003051</v>
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.020586</v>
+        <v>0.018264</v>
       </c>
       <c r="C106" s="3" t="n">
         <v>-0.013137</v>
@@ -2877,10 +2877,10 @@
         <v>0.00554</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>0</v>
+        <v>0.364911</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>0</v>
+        <v>5.34324</v>
       </c>
       <c r="F107" s="1" t="inlineStr">
         <is>
@@ -2949,10 +2949,10 @@
         <v>0</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.138903</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.713789</v>
       </c>
       <c r="F110" s="1" t="inlineStr">
         <is>
@@ -2973,10 +2973,10 @@
         <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.007642</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.01497</v>
       </c>
       <c r="F111" s="1" t="inlineStr">
         <is>
@@ -3093,10 +3093,10 @@
         <v>0</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-0.48304</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0</v>
+        <v>-0.245368</v>
       </c>
       <c r="F116" s="1" t="inlineStr">
         <is>
@@ -3533,10 +3533,10 @@
         <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.007642</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.01497</v>
       </c>
       <c r="F134" s="1" t="inlineStr">
         <is>
@@ -3557,10 +3557,10 @@
         <v>-0.128032</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-12.333707</v>
+        <v>-12.341349</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-19.646304</v>
+        <v>-19.661274</v>
       </c>
       <c r="F135" s="1" t="inlineStr">
         <is>
@@ -8412,7 +8412,11 @@
           <t>Interest accretion expense (note 14)</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
@@ -8451,7 +8455,11 @@
           <t>Share-based payment expense (note 17)</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>
@@ -9384,7 +9392,11 @@
           <t>Purchase of equipment (note 12)</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
           <t>-</t>
@@ -9423,7 +9435,11 @@
           <t>Purchase of intangible assets (note 13)</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
           <t>-</t>
@@ -11214,7 +11230,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E185" s="5" t="n">
         <v>-0.002322</v>
       </c>
@@ -13214,7 +13234,11 @@
           <t>Directors fees 4 -</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr">
         <is>
           <t>-</t>
@@ -14267,7 +14291,11 @@
           <t>Directors fees 4</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr"/>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E258" t="inlineStr">
         <is>
           <t>-</t>
